--- a/saida/Estudo_Hedge_Cafe_ICF.xlsx
+++ b/saida/Estudo_Hedge_Cafe_ICF.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Opcoes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Estruturas" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Programa de hedge" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Breakeven opcoes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -184,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -262,6 +263,8 @@
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5329,4 +5332,1394 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:M48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Breakeven das opcoes - a partir de que preco a protecao paga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Responde: qual strike vale mais a pena, e a partir de que ICF a estrutura comeca a pagar. Todas as opcoes calculadas para a razao de hedge de 100%, para comparar limpo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Referencias</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>ICF - futuro (US$/saca)</t>
+        </is>
+      </c>
+      <c r="D6" s="29">
+        <f>Parametros!C13</f>
+        <v/>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>MARGEM COMERCIAL HOJE (R$/saca)</t>
+        </is>
+      </c>
+      <c r="J6" s="41">
+        <f>$D$6*$D$10+$D$12-$D$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Volatilidade implicita</t>
+        </is>
+      </c>
+      <c r="D7" s="20">
+        <f>Parametros!C28</f>
+        <v/>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Preco de equilibrio do negocio (ICF que zera a margem)</t>
+        </is>
+      </c>
+      <c r="J7" s="51">
+        <f>($D$11-$D$12)/$D$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Prazo (anos)</t>
+        </is>
+      </c>
+      <c r="D8" s="30">
+        <f>Parametros!C29</f>
+        <v/>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Queda que ja zera o lucro dele</t>
+        </is>
+      </c>
+      <c r="J8" s="52">
+        <f>IF($D$6=0,0,$J$7/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>&lt;- este e o numero mais importante da aba: define de quanta queda ele precisa se proteger de verdade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Juros (a.a.)</t>
+        </is>
+      </c>
+      <c r="D9" s="39">
+        <f>Parametros!C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Cambio no vencimento</t>
+        </is>
+      </c>
+      <c r="D10" s="30">
+        <f>Parametros!C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Custo de compra + carrego (R$/saca)</t>
+        </is>
+      </c>
+      <c r="D11" s="31">
+        <f>Parametros!C8+Parametros!C10*Parametros!C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Basis de venda (R$/saca)</t>
+        </is>
+      </c>
+      <c r="D12" s="31">
+        <f>Parametros!C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>A) PUTS - comprar seguro contra queda</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="48" customHeight="1">
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>% do
+futuro</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>Strike
+(US$)</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Premio
+(US$)</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Premio
+(R$/saca)</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>% da
+margem</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>Paga a
+partir de
+(US$)</t>
+        </is>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>Breakeven
+(US$)</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>Queda ate o
+breakeven</t>
+        </is>
+      </c>
+      <c r="J15" s="33" t="inlineStr">
+        <is>
+          <t>PISO de
+margem
+(R$/saca)</t>
+        </is>
+      </c>
+      <c r="K15" s="33" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="L15" s="33" t="inlineStr">
+        <is>
+          <t>Veredito</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="15" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="C16" s="35">
+        <f>ROUND($D$6*B16/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D16" s="35">
+        <f>EXP(-$D$9*$D$8)*(C16*NORMSDIST(-(((LN($D$6/C16)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C16)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="27">
+        <f>D16*$D$10</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>IF($J$6&lt;=0,"",E16/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G16" s="35">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="H16" s="40">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="I16" s="38">
+        <f>IF($D$6=0,0,H16/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J16" s="41">
+        <f>C16*$D$10+$D$12-$D$11-E16</f>
+        <v/>
+      </c>
+      <c r="K16" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C16)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L16" s="47">
+        <f>IF(J16&gt;0,"Piso POSITIVO - protege o lucro",IF(F16&gt;1,"INVIAVEL - premio maior que a margem",IF(F16&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M16" s="46" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C17" s="35">
+        <f>ROUND($D$6*B17/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D17" s="35">
+        <f>EXP(-$D$9*$D$8)*(C17*NORMSDIST(-(((LN($D$6/C17)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C17)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>D17*$D$10</f>
+        <v/>
+      </c>
+      <c r="F17" s="24">
+        <f>IF($J$6&lt;=0,"",E17/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G17" s="35">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="H17" s="40">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="I17" s="38">
+        <f>IF($D$6=0,0,H17/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J17" s="41">
+        <f>C17*$D$10+$D$12-$D$11-E17</f>
+        <v/>
+      </c>
+      <c r="K17" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C17)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L17" s="47">
+        <f>IF(J17&gt;0,"Piso POSITIVO - protege o lucro",IF(F17&gt;1,"INVIAVEL - premio maior que a margem",IF(F17&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M17" s="46" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C18" s="35">
+        <f>ROUND($D$6*B18/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D18" s="35">
+        <f>EXP(-$D$9*$D$8)*(C18*NORMSDIST(-(((LN($D$6/C18)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C18)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>D18*$D$10</f>
+        <v/>
+      </c>
+      <c r="F18" s="24">
+        <f>IF($J$6&lt;=0,"",E18/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G18" s="35">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="H18" s="40">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="I18" s="38">
+        <f>IF($D$6=0,0,H18/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J18" s="41">
+        <f>C18*$D$10+$D$12-$D$11-E18</f>
+        <v/>
+      </c>
+      <c r="K18" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C18)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L18" s="47">
+        <f>IF(J18&gt;0,"Piso POSITIVO - protege o lucro",IF(F18&gt;1,"INVIAVEL - premio maior que a margem",IF(F18&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M18" s="46" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C19" s="35">
+        <f>ROUND($D$6*B19/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D19" s="35">
+        <f>EXP(-$D$9*$D$8)*(C19*NORMSDIST(-(((LN($D$6/C19)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C19)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>D19*$D$10</f>
+        <v/>
+      </c>
+      <c r="F19" s="24">
+        <f>IF($J$6&lt;=0,"",E19/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G19" s="35">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="H19" s="40">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="I19" s="38">
+        <f>IF($D$6=0,0,H19/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J19" s="41">
+        <f>C19*$D$10+$D$12-$D$11-E19</f>
+        <v/>
+      </c>
+      <c r="K19" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C19)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L19" s="47">
+        <f>IF(J19&gt;0,"Piso POSITIVO - protege o lucro",IF(F19&gt;1,"INVIAVEL - premio maior que a margem",IF(F19&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M19" s="46" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C20" s="35">
+        <f>ROUND($D$6*B20/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D20" s="35">
+        <f>EXP(-$D$9*$D$8)*(C20*NORMSDIST(-(((LN($D$6/C20)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C20)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>D20*$D$10</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
+        <f>IF($J$6&lt;=0,"",E20/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G20" s="35">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="H20" s="40">
+        <f>C20-D20</f>
+        <v/>
+      </c>
+      <c r="I20" s="38">
+        <f>IF($D$6=0,0,H20/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J20" s="41">
+        <f>C20*$D$10+$D$12-$D$11-E20</f>
+        <v/>
+      </c>
+      <c r="K20" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C20)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L20" s="47">
+        <f>IF(J20&gt;0,"Piso POSITIVO - protege o lucro",IF(F20&gt;1,"INVIAVEL - premio maior que a margem",IF(F20&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M20" s="46" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="35">
+        <f>ROUND($D$6*B21/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D21" s="35">
+        <f>EXP(-$D$9*$D$8)*(C21*NORMSDIST(-(((LN($D$6/C21)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C21)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E21" s="27">
+        <f>D21*$D$10</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>IF($J$6&lt;=0,"",E21/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G21" s="35">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="H21" s="40">
+        <f>C21-D21</f>
+        <v/>
+      </c>
+      <c r="I21" s="38">
+        <f>IF($D$6=0,0,H21/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J21" s="41">
+        <f>C21*$D$10+$D$12-$D$11-E21</f>
+        <v/>
+      </c>
+      <c r="K21" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C21)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L21" s="47">
+        <f>IF(J21&gt;0,"Piso POSITIVO - protege o lucro",IF(F21&gt;1,"INVIAVEL - premio maior que a margem",IF(F21&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M21" s="46" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="C22" s="35">
+        <f>ROUND($D$6*B22/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D22" s="35">
+        <f>EXP(-$D$9*$D$8)*(C22*NORMSDIST(-(((LN($D$6/C22)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C22)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="27">
+        <f>D22*$D$10</f>
+        <v/>
+      </c>
+      <c r="F22" s="24">
+        <f>IF($J$6&lt;=0,"",E22/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G22" s="35">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="H22" s="40">
+        <f>C22-D22</f>
+        <v/>
+      </c>
+      <c r="I22" s="38">
+        <f>IF($D$6=0,0,H22/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J22" s="41">
+        <f>C22*$D$10+$D$12-$D$11-E22</f>
+        <v/>
+      </c>
+      <c r="K22" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C22)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L22" s="47">
+        <f>IF(J22&gt;0,"Piso POSITIVO - protege o lucro",IF(F22&gt;1,"INVIAVEL - premio maior que a margem",IF(F22&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M22" s="46" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C23" s="35">
+        <f>ROUND($D$6*B23/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D23" s="35">
+        <f>EXP(-$D$9*$D$8)*(C23*NORMSDIST(-(((LN($D$6/C23)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C23)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="27">
+        <f>D23*$D$10</f>
+        <v/>
+      </c>
+      <c r="F23" s="24">
+        <f>IF($J$6&lt;=0,"",E23/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G23" s="35">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="H23" s="40">
+        <f>C23-D23</f>
+        <v/>
+      </c>
+      <c r="I23" s="38">
+        <f>IF($D$6=0,0,H23/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J23" s="41">
+        <f>C23*$D$10+$D$12-$D$11-E23</f>
+        <v/>
+      </c>
+      <c r="K23" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C23)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L23" s="47">
+        <f>IF(J23&gt;0,"Piso POSITIVO - protege o lucro",IF(F23&gt;1,"INVIAVEL - premio maior que a margem",IF(F23&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M23" s="46" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="C24" s="35">
+        <f>ROUND($D$6*B24/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D24" s="35">
+        <f>EXP(-$D$9*$D$8)*(C24*NORMSDIST(-(((LN($D$6/C24)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C24)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="27">
+        <f>D24*$D$10</f>
+        <v/>
+      </c>
+      <c r="F24" s="24">
+        <f>IF($J$6&lt;=0,"",E24/$J$6)</f>
+        <v/>
+      </c>
+      <c r="G24" s="35">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="H24" s="40">
+        <f>C24-D24</f>
+        <v/>
+      </c>
+      <c r="I24" s="38">
+        <f>IF($D$6=0,0,H24/$D$6-1)</f>
+        <v/>
+      </c>
+      <c r="J24" s="41">
+        <f>C24*$D$10+$D$12-$D$11-E24</f>
+        <v/>
+      </c>
+      <c r="K24" s="21">
+        <f>-EXP(-$D$9*$D$8)*NORMSDIST(-((LN($D$6/C24)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))</f>
+        <v/>
+      </c>
+      <c r="L24" s="47">
+        <f>IF(J24&gt;0,"Piso POSITIVO - protege o lucro",IF(F24&gt;1,"INVIAVEL - premio maior que a margem",IF(F24&gt;0.5,"Caro - come mais de metade da margem","Piso negativo, mas premio suportavel")))</f>
+        <v/>
+      </c>
+      <c r="M24" s="46" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Leitura: 'Paga a partir de' = onde a put comeca a ter valor de exercicio. 'Breakeven' = onde ela ja cobriu o premio. 'PISO de margem' negativo significa que a put limita o prejuizo, mas nao salva o lucro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>B) COLLARS - put comprada financiada pela call vendida</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>% put</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>Strike
+put (US$)</t>
+        </is>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>% call</t>
+        </is>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>Strike
+call (US$)</t>
+        </is>
+      </c>
+      <c r="F29" s="33" t="inlineStr">
+        <is>
+          <t>Premio put
+(US$)</t>
+        </is>
+      </c>
+      <c r="G29" s="33" t="inlineStr">
+        <is>
+          <t>Premio call
+(US$)</t>
+        </is>
+      </c>
+      <c r="H29" s="33" t="inlineStr">
+        <is>
+          <t>Custo liq.
+(R$/saca)</t>
+        </is>
+      </c>
+      <c r="I29" s="33" t="inlineStr">
+        <is>
+          <t>% da
+margem</t>
+        </is>
+      </c>
+      <c r="J29" s="33" t="inlineStr">
+        <is>
+          <t>Breakeven
+(US$)</t>
+        </is>
+      </c>
+      <c r="K29" s="33" t="inlineStr">
+        <is>
+          <t>PISO de
+margem
+(R$/saca)</t>
+        </is>
+      </c>
+      <c r="L29" s="33" t="inlineStr">
+        <is>
+          <t>TETO de
+margem
+(R$/saca)</t>
+        </is>
+      </c>
+      <c r="M29" s="33" t="inlineStr">
+        <is>
+          <t>Veredito</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C30" s="35">
+        <f>ROUND($D$6*B30/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E30" s="35">
+        <f>ROUND($D$6*D30/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F30" s="35">
+        <f>EXP(-$D$9*$D$8)*(C30*NORMSDIST(-(((LN($D$6/C30)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C30)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G30" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E30)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E30*NORMSDIST((((LN($D$6/E30)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="17">
+        <f>(F30-G30)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I30" s="24">
+        <f>IF($J$6&lt;=0,"",H30/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J30" s="35">
+        <f>C30-(F30-G30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="41">
+        <f>C30*$D$10+$D$12-$D$11-H30</f>
+        <v/>
+      </c>
+      <c r="L30" s="27">
+        <f>E30*$D$10+$D$12-$D$11-H30</f>
+        <v/>
+      </c>
+      <c r="M30" s="47">
+        <f>IF(AND(K30&gt;0,H30&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K30&gt;0,"BOM - piso positivo (margem garantida)",IF(H30&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C31" s="35">
+        <f>ROUND($D$6*B31/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E31" s="35">
+        <f>ROUND($D$6*D31/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F31" s="35">
+        <f>EXP(-$D$9*$D$8)*(C31*NORMSDIST(-(((LN($D$6/C31)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C31)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G31" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E31)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E31*NORMSDIST((((LN($D$6/E31)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>(F31-G31)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I31" s="24">
+        <f>IF($J$6&lt;=0,"",H31/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J31" s="35">
+        <f>C31-(F31-G31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="41">
+        <f>C31*$D$10+$D$12-$D$11-H31</f>
+        <v/>
+      </c>
+      <c r="L31" s="27">
+        <f>E31*$D$10+$D$12-$D$11-H31</f>
+        <v/>
+      </c>
+      <c r="M31" s="47">
+        <f>IF(AND(K31&gt;0,H31&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K31&gt;0,"BOM - piso positivo (margem garantida)",IF(H31&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C32" s="35">
+        <f>ROUND($D$6*B32/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E32" s="35">
+        <f>ROUND($D$6*D32/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F32" s="35">
+        <f>EXP(-$D$9*$D$8)*(C32*NORMSDIST(-(((LN($D$6/C32)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C32)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G32" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E32)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E32*NORMSDIST((((LN($D$6/E32)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>(F32-G32)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I32" s="24">
+        <f>IF($J$6&lt;=0,"",H32/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J32" s="35">
+        <f>C32-(F32-G32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="41">
+        <f>C32*$D$10+$D$12-$D$11-H32</f>
+        <v/>
+      </c>
+      <c r="L32" s="27">
+        <f>E32*$D$10+$D$12-$D$11-H32</f>
+        <v/>
+      </c>
+      <c r="M32" s="47">
+        <f>IF(AND(K32&gt;0,H32&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K32&gt;0,"BOM - piso positivo (margem garantida)",IF(H32&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C33" s="35">
+        <f>ROUND($D$6*B33/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E33" s="35">
+        <f>ROUND($D$6*D33/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F33" s="35">
+        <f>EXP(-$D$9*$D$8)*(C33*NORMSDIST(-(((LN($D$6/C33)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C33)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G33" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E33)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E33*NORMSDIST((((LN($D$6/E33)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>(F33-G33)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I33" s="24">
+        <f>IF($J$6&lt;=0,"",H33/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J33" s="35">
+        <f>C33-(F33-G33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="41">
+        <f>C33*$D$10+$D$12-$D$11-H33</f>
+        <v/>
+      </c>
+      <c r="L33" s="27">
+        <f>E33*$D$10+$D$12-$D$11-H33</f>
+        <v/>
+      </c>
+      <c r="M33" s="47">
+        <f>IF(AND(K33&gt;0,H33&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K33&gt;0,"BOM - piso positivo (margem garantida)",IF(H33&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C34" s="35">
+        <f>ROUND($D$6*B34/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E34" s="35">
+        <f>ROUND($D$6*D34/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F34" s="35">
+        <f>EXP(-$D$9*$D$8)*(C34*NORMSDIST(-(((LN($D$6/C34)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C34)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G34" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E34)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E34*NORMSDIST((((LN($D$6/E34)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>(F34-G34)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I34" s="24">
+        <f>IF($J$6&lt;=0,"",H34/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J34" s="35">
+        <f>C34-(F34-G34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="41">
+        <f>C34*$D$10+$D$12-$D$11-H34</f>
+        <v/>
+      </c>
+      <c r="L34" s="27">
+        <f>E34*$D$10+$D$12-$D$11-H34</f>
+        <v/>
+      </c>
+      <c r="M34" s="47">
+        <f>IF(AND(K34&gt;0,H34&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K34&gt;0,"BOM - piso positivo (margem garantida)",IF(H34&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C35" s="35">
+        <f>ROUND($D$6*B35/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E35" s="35">
+        <f>ROUND($D$6*D35/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F35" s="35">
+        <f>EXP(-$D$9*$D$8)*(C35*NORMSDIST(-(((LN($D$6/C35)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C35)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G35" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E35)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E35*NORMSDIST((((LN($D$6/E35)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>(F35-G35)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I35" s="24">
+        <f>IF($J$6&lt;=0,"",H35/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J35" s="35">
+        <f>C35-(F35-G35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="41">
+        <f>C35*$D$10+$D$12-$D$11-H35</f>
+        <v/>
+      </c>
+      <c r="L35" s="27">
+        <f>E35*$D$10+$D$12-$D$11-H35</f>
+        <v/>
+      </c>
+      <c r="M35" s="47">
+        <f>IF(AND(K35&gt;0,H35&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K35&gt;0,"BOM - piso positivo (margem garantida)",IF(H35&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="15" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="C36" s="35">
+        <f>ROUND($D$6*B36/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E36" s="35">
+        <f>ROUND($D$6*D36/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F36" s="35">
+        <f>EXP(-$D$9*$D$8)*(C36*NORMSDIST(-(((LN($D$6/C36)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C36)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G36" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E36)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E36*NORMSDIST((((LN($D$6/E36)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>(F36-G36)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I36" s="24">
+        <f>IF($J$6&lt;=0,"",H36/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J36" s="35">
+        <f>C36-(F36-G36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="41">
+        <f>C36*$D$10+$D$12-$D$11-H36</f>
+        <v/>
+      </c>
+      <c r="L36" s="27">
+        <f>E36*$D$10+$D$12-$D$11-H36</f>
+        <v/>
+      </c>
+      <c r="M36" s="47">
+        <f>IF(AND(K36&gt;0,H36&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K36&gt;0,"BOM - piso positivo (margem garantida)",IF(H36&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="35">
+        <f>ROUND($D$6*B37/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E37" s="35">
+        <f>ROUND($D$6*D37/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F37" s="35">
+        <f>EXP(-$D$9*$D$8)*(C37*NORMSDIST(-(((LN($D$6/C37)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C37)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G37" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E37)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E37*NORMSDIST((((LN($D$6/E37)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>(F37-G37)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I37" s="24">
+        <f>IF($J$6&lt;=0,"",H37/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J37" s="35">
+        <f>C37-(F37-G37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="41">
+        <f>C37*$D$10+$D$12-$D$11-H37</f>
+        <v/>
+      </c>
+      <c r="L37" s="27">
+        <f>E37*$D$10+$D$12-$D$11-H37</f>
+        <v/>
+      </c>
+      <c r="M37" s="47">
+        <f>IF(AND(K37&gt;0,H37&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K37&gt;0,"BOM - piso positivo (margem garantida)",IF(H37&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="35">
+        <f>ROUND($D$6*B38/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E38" s="35">
+        <f>ROUND($D$6*D38/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F38" s="35">
+        <f>EXP(-$D$9*$D$8)*(C38*NORMSDIST(-(((LN($D$6/C38)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C38)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G38" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E38)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E38*NORMSDIST((((LN($D$6/E38)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>(F38-G38)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I38" s="24">
+        <f>IF($J$6&lt;=0,"",H38/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J38" s="35">
+        <f>C38-(F38-G38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="41">
+        <f>C38*$D$10+$D$12-$D$11-H38</f>
+        <v/>
+      </c>
+      <c r="L38" s="27">
+        <f>E38*$D$10+$D$12-$D$11-H38</f>
+        <v/>
+      </c>
+      <c r="M38" s="47">
+        <f>IF(AND(K38&gt;0,H38&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K38&gt;0,"BOM - piso positivo (margem garantida)",IF(H38&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="35">
+        <f>ROUND($D$6*B39/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E39" s="35">
+        <f>ROUND($D$6*D39/5,0)*5</f>
+        <v/>
+      </c>
+      <c r="F39" s="35">
+        <f>EXP(-$D$9*$D$8)*(C39*NORMSDIST(-(((LN($D$6/C39)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8))))-$D$6*NORMSDIST(-((LN($D$6/C39)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="G39" s="35">
+        <f>EXP(-$D$9*$D$8)*($D$6*NORMSDIST(((LN($D$6/E39)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8))))-E39*NORMSDIST((((LN($D$6/E39)+0.5*$D$7^2*$D$8)/($D$7*SQRT($D$8)))-($D$7*SQRT($D$8)))))</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>(F39-G39)*$D$10</f>
+        <v/>
+      </c>
+      <c r="I39" s="24">
+        <f>IF($J$6&lt;=0,"",H39/$J$6)</f>
+        <v/>
+      </c>
+      <c r="J39" s="35">
+        <f>C39-(F39-G39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="41">
+        <f>C39*$D$10+$D$12-$D$11-H39</f>
+        <v/>
+      </c>
+      <c r="L39" s="27">
+        <f>E39*$D$10+$D$12-$D$11-H39</f>
+        <v/>
+      </c>
+      <c r="M39" s="47">
+        <f>IF(AND(K39&gt;0,H39&lt;=0),"OTIMO - piso positivo e entra com credito",IF(K39&gt;0,"BOM - piso positivo (margem garantida)",IF(H39&lt;=0,"Entra com credito, mas piso negativo","Piso negativo - avaliar")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Melhor piso de margem entre os collars</t>
+        </is>
+      </c>
+      <c r="G41" s="41">
+        <f>MAX(K30:K39)</f>
+        <v/>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Strike da put desse collar</t>
+        </is>
+      </c>
+      <c r="J41" s="40">
+        <f>INDEX(C30:C39,MATCH(MAX(K30:K39),K30:K39,0))</f>
+        <v/>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>Strike da call</t>
+        </is>
+      </c>
+      <c r="L41" s="40">
+        <f>INDEX(E30:E39,MATCH(MAX(K30:K39),K30:K39,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Collar mais barato (menor custo liquido)</t>
+        </is>
+      </c>
+      <c r="G42" s="41">
+        <f>MIN(H30:H39)</f>
+        <v/>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>Negativo = entra com credito no caixa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>RESSALVA IMPORTANTE SOBRE O MODELO</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr"/>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>Este modelo usa UMA volatilidade unica para todos os strikes (vol plana). O mercado real tem 'skew': puts e calls fora do dinheiro negociam com vols diferentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>Consequencia pratica: collars que aparecem aqui 'entrando com credito' podem virar custo na tela real, se a put estiver com vol maior que a call. No cafe costuma ocorrer o contrario (call com vol maior, por risco de quebra de safra), o que favoreceria o credito - mas isso precisa ser CONFERIDO, nao presumido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>Antes de prometer qualquer estrutura ao cliente: peca a vol de cada strike a mesa da XP e substitua a celula D7 por vencimento/strike, ou refaca a conta com os premios de tela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>Os strikes calculados aqui sao arredondados de 5 em 5 dolares e podem nao existir listados. Confirme quais strikes tem oferta firme.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="C45:M45"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="C47:M47"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="C46:M46"/>
+    <mergeCell ref="B26:M26"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="C48:M48"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="B41:F41"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>